--- a/resources/templates/invoices/reference/領収書.xlsx
+++ b/resources/templates/invoices/reference/領収書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林智哉\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186EEA55-83F4-45B1-A51B-CAEE54031A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A52FE26-826D-460D-8068-525C7D07455A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,7 +705,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -837,11 +837,6 @@
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -849,23 +844,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="6" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -882,8 +862,60 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1065,7 +1097,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -1121,7 +1153,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -1309,7 +1341,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -1365,7 +1397,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -1553,7 +1585,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -1609,7 +1641,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -1797,7 +1829,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -1853,7 +1885,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -2046,7 +2078,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -2102,7 +2134,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -2290,7 +2322,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -2346,7 +2378,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -2534,7 +2566,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -2590,7 +2622,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -2778,7 +2810,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -2834,7 +2866,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -3027,7 +3059,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -3083,7 +3115,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -3271,7 +3303,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -3327,7 +3359,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -3515,7 +3547,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -3571,7 +3603,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -3759,7 +3791,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -3815,7 +3847,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -4008,7 +4040,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -4064,7 +4096,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -4252,7 +4284,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -4308,7 +4340,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -4496,7 +4528,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -4552,7 +4584,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -4740,7 +4772,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -4796,7 +4828,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -4989,7 +5021,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -5045,7 +5077,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -5233,7 +5265,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -5289,7 +5321,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -5477,7 +5509,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -5533,7 +5565,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -5721,7 +5753,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -5777,7 +5809,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -5970,7 +6002,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -6026,7 +6058,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -6214,7 +6246,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -6270,7 +6302,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -6458,7 +6490,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -6514,7 +6546,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -6702,7 +6734,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -6758,7 +6790,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -6951,7 +6983,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -7007,7 +7039,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -7195,7 +7227,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -7251,7 +7283,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -7439,7 +7471,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -7495,7 +7527,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -7683,7 +7715,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -7739,7 +7771,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -7932,7 +7964,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -7988,7 +8020,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
             <a:stretch>
@@ -8176,7 +8208,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -8232,7 +8264,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
@@ -8420,7 +8452,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -8476,7 +8508,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
+        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
             <a:stretch>
@@ -8664,7 +8696,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -8720,7 +8752,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" xmlns="" Requires="ma">
+        <mc:Choice xmlns="" xmlns:ma="http://schemas.microsoft.com/office/mac/drawingml/2008/main" Requires="ma">
           <xdr:blipFill>
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
             <a:stretch>
@@ -9088,113 +9120,176 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:7">
-      <c r="F3" s="26" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="18"/>
+      <c r="G3" s="36"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="8.15" customHeight="1">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+    </row>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="30" t="s">
+      <c r="A6" s="34"/>
+      <c r="B6" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="34"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
-      <c r="B7" s="5"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
-      <c r="B9" s="15"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+    </row>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
-      <c r="B12" s="1"/>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
-      <c r="B13" s="1"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="16" customHeight="1"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+    </row>
+    <row r="14" spans="1:7" ht="16" customHeight="1">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+    </row>
     <row r="15" spans="1:7" ht="18" customHeight="1">
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="C15" s="34"/>
+      <c r="D15" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1">
-      <c r="B16" s="3"/>
-      <c r="D16" s="25" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="53" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" ht="18" customHeight="1">
-      <c r="B17" s="4" t="s">
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1">
+      <c r="A17" s="34"/>
+      <c r="B17" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-    </row>
-    <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+    </row>
+    <row r="19" spans="1:7" ht="14.15" customHeight="1">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9238,67 +9333,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>10000</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -9333,16 +9428,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9388,67 +9483,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>55500</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -9484,16 +9579,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9539,67 +9634,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>118000</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -9635,16 +9730,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9690,67 +9785,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>96000</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -9786,16 +9881,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9841,67 +9936,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>80000</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -9937,16 +10032,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9992,67 +10087,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>66000</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -10088,16 +10183,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -10143,67 +10238,67 @@
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="23.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="8.15" customHeight="1"/>
     <row r="6" spans="1:7" ht="48" customHeight="1">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="37">
+      <c r="D7" s="29">
         <v>42000</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.15" customHeight="1">
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1"/>
     <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:7" ht="25" customHeight="1">
       <c r="B12" s="1"/>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1">
       <c r="B13" s="1"/>
@@ -10239,16 +10334,16 @@
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="2:6" ht="14.15" customHeight="1">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
